--- a/dataset/test/valutazione risposte.xlsx
+++ b/dataset/test/valutazione risposte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Massimo\Desktop\Università\Progettazione e Produzione Multimediale\Tesi\Elaborati\Ufficiale\Progetto\dataset\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F486BA5D-79FD-466A-B2BA-F15FAFD797F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50528DD0-B8C1-43C1-AE46-180B59F4D370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
